--- a/data/trans_bre/P1416-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1416-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-4,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-63,36%</t>
+          <t>-43,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,69</t>
+          <t>-4,23; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,29</t>
+          <t>-1,27; 9,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 8,05</t>
+          <t>-1,49; 8,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -3,03</t>
+          <t>-10,28; 0,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 114,62</t>
+          <t>-57,6; 97,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 187,05</t>
+          <t>-15,08; 183,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 174,43</t>
+          <t>-19,87; 207,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-81,33; -31,74</t>
+          <t>-70,01; 5,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 7,77</t>
+          <t>0,2; 7,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,56</t>
+          <t>-2,38; 4,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,37</t>
+          <t>0,97; 6,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,76</t>
+          <t>-4,01; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 166,33</t>
+          <t>1,51; 155,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 98,2</t>
+          <t>-29,4; 102,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 264,96</t>
+          <t>11,26; 276,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 52,75</t>
+          <t>-25,5; 49,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,42</t>
+          <t>-0,95; 6,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,38</t>
+          <t>0,1; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,57</t>
+          <t>-3,33; 2,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,76</t>
+          <t>-3,49; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 238,42</t>
+          <t>-19,41; 225,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 334,68</t>
+          <t>-9,19; 296,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 93,19</t>
+          <t>-55,24; 100,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 92,45</t>
+          <t>-30,17; 83,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-16,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 7,1</t>
+          <t>-1,53; 7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,75</t>
+          <t>-0,14; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,52</t>
+          <t>-0,46; 7,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 2,27</t>
+          <t>-3,57; 4,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 105,0</t>
+          <t>-16,24; 111,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 230,25</t>
+          <t>-5,41; 243,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 203,31</t>
+          <t>-14,33; 200,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 73,87</t>
+          <t>-46,67; 153,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,45</t>
+          <t>-2,17; 10,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 10,82</t>
+          <t>-1,52; 9,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 7,98</t>
+          <t>-1,75; 8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,43</t>
+          <t>-3,12; 6,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 166,67</t>
+          <t>-21,62; 175,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 204,44</t>
+          <t>-15,07; 180,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 254,93</t>
+          <t>-25,02; 250,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 82,93</t>
+          <t>-24,61; 93,39</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 8,39</t>
+          <t>-0,38; 7,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,06</t>
+          <t>-4,56; 3,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,47</t>
+          <t>-3,55; 5,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 9,4</t>
+          <t>-1,57; 9,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 245,9</t>
+          <t>-10,36; 216,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 119,56</t>
+          <t>-55,56; 107,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,15; 131,93</t>
+          <t>-43,07; 123,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 89,08</t>
+          <t>-9,65; 87,09</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,68</t>
+          <t>-0,55; 4,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,63</t>
+          <t>0,05; 4,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,09</t>
+          <t>2,44; 7,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 6,57</t>
+          <t>1,28; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 146,84</t>
+          <t>-14,55; 139,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 188,99</t>
+          <t>-1,21; 200,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,17; 343,78</t>
+          <t>54,54; 359,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 59,92</t>
+          <t>7,37; 87,69</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120,36%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,37</t>
+          <t>0,06; 6,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,45</t>
+          <t>-1,12; 3,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,83</t>
+          <t>0,37; 5,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,9</t>
+          <t>1,44; 7,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 83,78</t>
+          <t>-1,76; 82,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 86,86</t>
+          <t>-18,16; 89,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 114,02</t>
+          <t>4,69; 111,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,58; 381,55</t>
+          <t>16,71; 139,91</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,21</t>
+          <t>1,51; 4,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,39</t>
+          <t>1,08; 3,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,21</t>
+          <t>1,78; 4,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,48</t>
+          <t>0,81; 3,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,84; 69,12</t>
+          <t>21,13; 68,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 72,17</t>
+          <t>18,22; 74,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,34; 94,45</t>
+          <t>31,45; 93,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 43,74</t>
+          <t>7,61; 42,38</t>
         </is>
       </c>
     </row>
